--- a/docs/downloads/10/tbl_menaces_marovoay_tous.xlsx
+++ b/docs/downloads/10/tbl_menaces_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -399,7 +399,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -439,7 +439,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,7 +459,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1119,7 +1119,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
